--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2900.04</v>
+        <v>2884.19</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1223.59</v>
+        <v>1227.62</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>743.3200000000001</v>
+        <v>745.76</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1133.98</v>
+        <v>1142.16</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2421.51</v>
+        <v>2417.22</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1103.85</v>
+        <v>1099.3</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>787.49</v>
+        <v>791.55</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1333.08</v>
+        <v>1339.96</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1291.36</v>
+        <v>1300.48</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2253.18</v>
+        <v>2224.06</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1483.77</v>
+        <v>1464.93</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>9294.879999999999</v>
+        <v>9176.809999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1193.97</v>
+        <v>1188.97</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>764.02</v>
+        <v>760.8200000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2111.68</v>
+        <v>2087.24</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>808.02</v>
+        <v>807.37</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1524.84</v>
+        <v>1523.61</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>837.5</v>
+        <v>836.8200000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1934.19</v>
+        <v>1932.63</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2411.86</v>
+        <v>2418.26</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8505.139999999999</v>
+        <v>8527.690000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1674.82</v>
+        <v>1679.26</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2299.24</v>
+        <v>2305.34</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5558.83</v>
+        <v>5573.57</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1663.77</v>
+        <v>1668.18</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1178.32</v>
+        <v>1179.83</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1154.25</v>
+        <v>1155.73</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1155.73</v>
+        <v>1163.69</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>918.8</v>
+        <v>926.65</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>845.96</v>
+        <v>833.77</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2633.11</v>
+        <v>2627.93</v>
       </c>
     </row>
     <row r="33">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2578.86</v>
+        <v>2578.88</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1295.05</v>
+        <v>1296.85</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1107.93</v>
+        <v>1102.08</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4115.72</v>
+        <v>4093.98</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1374.21</v>
+        <v>1392.72</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>14121.33</v>
+        <v>14311.5</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>10225.2</v>
+        <v>10188.8</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5605.71</v>
+        <v>5644.74</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1162.72</v>
+        <v>1170.82</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4123.3</v>
+        <v>4150.45</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1520.04</v>
+        <v>1530.06</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4932.45</v>
+        <v>4964.93</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2162.11</v>
+        <v>2181.36</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8235.870000000001</v>
+        <v>8221.76</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1083.13</v>
+        <v>1081.27</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>5018.04</v>
+        <v>5010.66</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>815.02</v>
+        <v>810.58</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1451.21</v>
+        <v>1442.65</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1202.96</v>
+        <v>1209.19</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3156.84</v>
+        <v>3159.88</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1379.11</v>
+        <v>1380.44</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1386.35</v>
+        <v>1447.58</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>938.51</v>
+        <v>940.8200000000001</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1910.31</v>
+        <v>1915.01</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1276.88</v>
+        <v>1260.44</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1056.74</v>
+        <v>1043.13</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1570.39</v>
+        <v>1550.17</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>803.73</v>
+        <v>798.0599999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>924.58</v>
+        <v>918.0599999999999</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1497.27</v>
+        <v>1524.42</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>912.8099999999999</v>
+        <v>929.36</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8590.98</v>
+        <v>8746.74</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>770.62</v>
+        <v>784.59</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2655.21</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3983.9</v>
+        <v>3924.48</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3293.81</v>
+        <v>3279.62</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2127.33</v>
+        <v>2059.5</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1102.83</v>
+        <v>1073.79</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3234.73</v>
+        <v>3148.11</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>34061.84</v>
+        <v>34203.4</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2761.33</v>
+        <v>2784.77</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7003.6</v>
+        <v>7089.79</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2725.15</v>
+        <v>2761.43</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>905.87</v>
+        <v>917.9299999999999</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>821.95</v>
+        <v>832.89</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>968.53</v>
+        <v>992.37</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3461.18</v>
+        <v>3492.36</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1118.3</v>
+        <v>1124.32</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>804.4400000000001</v>
+        <v>808.77</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1417.77</v>
+        <v>1433.63</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>791.01</v>
+        <v>794.01</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>30293.65</v>
+        <v>30581.46</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2110.03</v>
+        <v>2125.75</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>982.86</v>
+        <v>978.55</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>792.76</v>
+        <v>789.29</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2252.1</v>
+        <v>2263.16</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>6008.86</v>
+        <v>6028.79</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1637.29</v>
+        <v>1642.73</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2364.72</v>
+        <v>2372.25</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>14606.39</v>
+        <v>14684.05</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>919.27</v>
+        <v>930.05</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1007.85</v>
+        <v>1019.68</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>5441.25</v>
+        <v>5544.7</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4053.15</v>
+        <v>4144.56</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>839.17</v>
+        <v>822.74</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2539.7</v>
+        <v>2502.07</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1576.34</v>
+        <v>1552.99</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5277.09</v>
+        <v>5198.91</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3392.64</v>
+        <v>3342.38</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1229.63</v>
+        <v>1234.43</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>841.58</v>
+        <v>844.86</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>792.92</v>
+        <v>794.73</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>790.72</v>
+        <v>777.96</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3611.64</v>
+        <v>3553.36</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1738.22</v>
+        <v>1710.35</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1518.24</v>
+        <v>1500.57</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,68 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2009.19</v>
+        <v>1998.05</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>5394-442-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>71.133.700-8</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>9558.85</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5338-900-CM25</t>
+          <t>1057402-25781-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>7.560.370-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2884.19</v>
+        <v>890.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1109692-269-CM25</t>
+          <t>5147-278-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1227.62</v>
+        <v>2552.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1988-74-CM25</t>
+          <t>5338-900-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.701.003-K</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>745.76</v>
+        <v>2884.19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1109692-273-CM25</t>
+          <t>1109692-269-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MARANGUNIC HERMANOS LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>80.586.800-7</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1142.16</v>
+        <v>1227.62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5394-774-CM25</t>
+          <t>1988-74-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>60.701.003-K</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2417.22</v>
+        <v>745.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3241-296-CM25</t>
+          <t>1109692-273-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,22 +834,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.102.028-7</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>MARANGUNIC HERMANOS LIMITADA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>80.586.800-7</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1099.3</v>
+        <v>1142.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1347-75-CM25</t>
+          <t>5394-774-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.002.492-0</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>791.55</v>
+        <v>2417.22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3130-4339-CM25</t>
+          <t>3241-296-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.102.028-7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1339.96</v>
+        <v>1099.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1109692-283-CM25</t>
+          <t>1347-75-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>61.002.492-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1300.48</v>
+        <v>791.55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1109692-286-CM25</t>
+          <t>3130-4339-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2224.06</v>
+        <v>1339.96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>855-258-CM25</t>
+          <t>1109692-283-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1464.93</v>
+        <v>1300.48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>855-259-CM25</t>
+          <t>1109692-286-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>9176.809999999999</v>
+        <v>2224.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3130-4461-CM25</t>
+          <t>855-258-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1188.97</v>
+        <v>1464.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4890-407-CM25</t>
+          <t>855-259-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.972.500-k</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región de Magallanes y la Antartica</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>760.8200000000001</v>
+        <v>9176.809999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1208985-120-CM25</t>
+          <t>4890-407-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.972.500-k</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>Subsecretaria de las Culturas y las Artes Región de Magallanes y la Antartica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2087.24</v>
+        <v>760.8200000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1057402-43526-CM25</t>
+          <t>3130-4461-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>807.37</v>
+        <v>1188.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2019-154-CM25</t>
+          <t>1208985-120-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1523.61</v>
+        <v>2087.24</v>
       </c>
     </row>
     <row r="19">
@@ -1673,7 +1673,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3268-926-CM25</t>
+          <t>2019-154-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2418.26</v>
+        <v>1523.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3268-927-CM25</t>
+          <t>1057402-43526-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8527.690000000001</v>
+        <v>807.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2019-158-CM25</t>
+          <t>3268-926-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.511.122-k</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1679.26</v>
+        <v>2418.26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1347-79-CM25</t>
+          <t>3268-927-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.002.492-0</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2305.34</v>
+        <v>8527.690000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2019-162-CM25</t>
+          <t>2019-158-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5573.57</v>
+        <v>1679.26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5394-857-CM25</t>
+          <t>1347-79-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.002.492-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1668.18</v>
+        <v>2305.34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2019-163-CM25</t>
+          <t>2019-162-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1179.83</v>
+        <v>5573.57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1208985-124-CM25</t>
+          <t>5394-857-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1155.73</v>
+        <v>1668.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1237328-811-CM25</t>
+          <t>2019-163-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>60.511.122-k</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ÚLTIMA ESPERANZA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>7.560.370-3</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1163.69</v>
+        <v>1179.83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1237328-827-CM25</t>
+          <t>1208985-124-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MARANGUNIC HERMANOS LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>80.586.800-7</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>926.65</v>
+        <v>1155.73</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057402-136-CM26</t>
+          <t>1237328-811-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>7.560.370-3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>833.77</v>
+        <v>1163.69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>548871-9-CM26</t>
+          <t>1237328-827-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.979.440-0</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>MARANGUNIC HERMANOS LIMITADA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
+          <t>80.586.800-7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2627.93</v>
+        <v>926.65</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1540-90-CM26</t>
+          <t>1057402-136-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>969.49</v>
+        <v>833.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1540-91-CM26</t>
+          <t>548871-9-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>61.979.440-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>Instituto de Prevision Social</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2578.88</v>
+        <v>2627.93</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5338-15-CM26</t>
+          <t>1540-90-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,22 +2542,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1296.85</v>
+        <v>969.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5020-1-CM26</t>
+          <t>1540-91-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>65.940.830-9</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1102.08</v>
+        <v>2578.88</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2983-8-CM26</t>
+          <t>5338-15-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4093.98</v>
+        <v>1296.85</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3617-2-CM26</t>
+          <t>5020-1-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>65.940.830-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1392.72</v>
+        <v>1102.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5338-31-CM26</t>
+          <t>2983-8-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>14311.5</v>
+        <v>4093.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1079445-22-CM26</t>
+          <t>3617-2-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.505.628-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XII ZONA</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>10188.8</v>
+        <v>1392.72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3166-32-CM26</t>
+          <t>5338-31-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>71.133.700-8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>5644.74</v>
+        <v>14311.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1162-27-CM26</t>
+          <t>1079445-22-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.505.628-8</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SECCIÓN COMPRAS XII ZONA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1170.82</v>
+        <v>10188.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3166-36-CM26</t>
+          <t>1162-27-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,22 +3030,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4150.45</v>
+        <v>1170.82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3166-33-CM26</t>
+          <t>3166-32-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>7.560.370-3</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1530.06</v>
+        <v>5644.74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3166-35-CM26</t>
+          <t>3166-33-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>7.560.370-3</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4964.93</v>
+        <v>1530.06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3166-48-CM26</t>
+          <t>3166-35-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2181.36</v>
+        <v>4964.93</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2348-88-CM26</t>
+          <t>3166-36-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>CENTRO DE ABASTECIMIENTO (M)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8221.76</v>
+        <v>4150.45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1162-23-CM26</t>
+          <t>3166-48-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,22 +3335,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CENTRO DE ABASTECIMIENTO (M)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>77.798.686-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1081.27</v>
+        <v>2181.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3166-76-CM26</t>
+          <t>2348-88-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.102.027-9</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (M)</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>5010.66</v>
+        <v>8221.76</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2354-55-CM26</t>
+          <t>1162-23-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>810.58</v>
+        <v>1081.27</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1162-31-CM26</t>
+          <t>3166-76-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,22 +3518,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.102.027-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CENTRO DE ABASTECIMIENTO (M)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1442.65</v>
+        <v>5010.66</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>935-56-CM26</t>
+          <t>2354-55-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1209.19</v>
+        <v>810.58</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2099-60-CM26</t>
+          <t>1162-31-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,22 +3640,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3159.88</v>
+        <v>1442.65</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2099-61-CM26</t>
+          <t>935-56-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1380.44</v>
+        <v>1209.19</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1208985-17-CM26</t>
+          <t>2099-60-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1447.58</v>
+        <v>3159.88</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5147-49-CM26</t>
+          <t>2099-61-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>940.8200000000001</v>
+        <v>1380.44</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>902977-6-CM26</t>
+          <t>1208985-17-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,22 +3884,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1915.01</v>
+        <v>1447.58</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3268-119-CM26</t>
+          <t>902977-6-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,22 +3945,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1260.44</v>
+        <v>1915.01</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3595-101-CM26</t>
+          <t>5147-49-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,22 +4006,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.251.400-9</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1043.13</v>
+        <v>940.8200000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>874750-90-CM26</t>
+          <t>3268-119-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1550.17</v>
+        <v>1260.44</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1162-40-CM26</t>
+          <t>3595-101-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,22 +4128,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.251.400-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RIO VERDE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>798.0599999999999</v>
+        <v>1043.13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057402-2609-CM26</t>
+          <t>874750-90-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>918.0599999999999</v>
+        <v>1550.17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1347-8-CM26</t>
+          <t>1162-40-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.002.492-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1524.42</v>
+        <v>798.0599999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1347-9-CM26</t>
+          <t>1057402-2609-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.002.492-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>929.36</v>
+        <v>918.0599999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1347-10-CM26</t>
+          <t>1347-8-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>8746.74</v>
+        <v>1524.42</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3638-112-CM26</t>
+          <t>1347-9-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4438,17 +4438,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.250.300-7</t>
+          <t>61.002.492-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE PORVENIR</t>
+          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>7.560.370-3</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>784.59</v>
+        <v>929.36</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3638-113-CM26</t>
+          <t>1347-10-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4499,17 +4499,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.250.300-7</t>
+          <t>61.002.492-0</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE PORVENIR</t>
+          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2703.35</v>
+        <v>8746.74</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1237328-101-CM26</t>
+          <t>3638-112-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,22 +4555,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>69.250.300-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>I.MUNICIPALIDAD DE PORVENIR</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>7.560.370-3</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3924.48</v>
+        <v>784.59</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1000813-73-CM26</t>
+          <t>3638-113-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,22 +4616,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>69.250.300-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>I.MUNICIPALIDAD DE PORVENIR</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3279.62</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1233613-701-CM26</t>
+          <t>1237328-101-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2059.5</v>
+        <v>3924.48</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5147-88-CM26</t>
+          <t>1000813-73-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,27 +4733,27 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.999.040-4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1073.79</v>
+        <v>3279.62</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4052-38-CM26</t>
+          <t>1233613-701-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.251.200-6</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>MARANGUNIC HERMANOS LIMITADA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>80.586.800-7</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3148.11</v>
+        <v>2059.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1237328-125-CM26</t>
+          <t>5147-88-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4860,22 +4860,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>70.931.900-0</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>34203.4</v>
+        <v>1073.79</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1540-882-CM26</t>
+          <t>4052-38-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>69.251.200-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>I MUNICIPALIDAD DE LAGUNA BLANCA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>MARANGUNIC HERMANOS LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>80.586.800-7</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2784.77</v>
+        <v>3148.11</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>874750-115-CM26</t>
+          <t>1237328-125-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>70.931.900-0</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>CORP MUNICIPAL DE PUNTA ARENAS PARA LA EDUCACION SALUD Y AT AL MENOR</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>7089.79</v>
+        <v>34203.4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5147-97-CM26</t>
+          <t>1540-882-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,22 +5043,22 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.251.600-1</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2761.43</v>
+        <v>2784.77</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3241-83-CM26</t>
+          <t>874750-115-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.102.028-7</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>917.9299999999999</v>
+        <v>7089.79</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1109692-96-CM26</t>
+          <t>5147-97-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>69.251.600-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>ILUSTRE MUNICIPALIDAD DE TIMAUKEL</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>7.560.370-3</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>832.89</v>
+        <v>2761.43</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1109692-101-CM26</t>
+          <t>3241-83-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>61.102.028-7</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>992.37</v>
+        <v>917.9299999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4627-7-CM26</t>
+          <t>1109692-96-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>7.560.370-3</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3492.36</v>
+        <v>832.89</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1233613-907-CM26</t>
+          <t>1109692-101-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>62.000.760-9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>1124.32</v>
+        <v>992.37</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1890-9-CM26</t>
+          <t>4627-7-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5404,12 +5404,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.941.900-6</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>808.77</v>
+        <v>3492.36</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4305-66-CM26</t>
+          <t>1233613-907-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1433.63</v>
+        <v>1124.32</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3866-60-CM26</t>
+          <t>1890-9-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,22 +5531,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.251.300-2</t>
+          <t>61.941.900-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>794.01</v>
+        <v>808.77</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1233613-1028-CM26</t>
+          <t>4305-66-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.980.960-2</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Magallanes</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>30581.46</v>
+        <v>1433.63</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>709129-16-CM26</t>
+          <t>3866-60-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,22 +5653,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.251.300-2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ministerio Publico</t>
+          <t>I MUNICIPALIDAD DE PRIMAVERA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2125.75</v>
+        <v>794.01</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1609-129-CM26</t>
+          <t>1233613-1028-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>978.55</v>
+        <v>30581.46</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>709129-19-CM26</t>
+          <t>709129-16-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>789.29</v>
+        <v>2125.75</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1000813-200-CM26</t>
+          <t>1609-129-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>2263.16</v>
+        <v>978.55</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>855-74-CM26</t>
+          <t>709129-19-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,22 +5897,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Ministerio Publico</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>6028.79</v>
+        <v>789.29</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1038-109-CM26</t>
+          <t>1000813-200-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.999.040-4</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1642.73</v>
+        <v>2263.16</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>661-15-CM26</t>
+          <t>855-74-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.802.012-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2372.25</v>
+        <v>6028.79</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>707427-28-CM26</t>
+          <t>1038-109-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,22 +6080,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>14684.05</v>
+        <v>1642.73</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057402-5960-CM26</t>
+          <t>661-15-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.802.012-6</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>Ministerio de Vivienda y Urbanismo</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>930.05</v>
+        <v>2372.25</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1609-155-CM26</t>
+          <t>707427-28-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1019.68</v>
+        <v>14684.05</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3130-6132-CM26</t>
+          <t>1057402-5960-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.102.029-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>5544.7</v>
+        <v>930.05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1540-1446-CM26</t>
+          <t>1609-155-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,22 +6324,22 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.607.904-2</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>4144.56</v>
+        <v>1019.68</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2099-266-CM26</t>
+          <t>3130-6132-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.102.029-5</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>HOSPITAL NAVAL CIRUJANO GUZMAN DE MAGALL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>LIBRERIA</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.567.094-2</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>822.74</v>
+        <v>5544.7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>855-99-CM26</t>
+          <t>1540-1446-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.607.904-2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PTO NATALES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2502.07</v>
+        <v>4144.56</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>855-100-CM26</t>
+          <t>2099-266-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,22 +6507,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LIBRERIA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.567.094-2</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1552.99</v>
+        <v>822.74</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>855-101-CM26</t>
+          <t>855-99-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5198.91</v>
+        <v>2502.07</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>855-102-CM26</t>
+          <t>855-100-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3342.38</v>
+        <v>1552.99</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1208985-87-CM26</t>
+          <t>855-101-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1234.43</v>
+        <v>5198.91</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1057402-7105-CM26</t>
+          <t>855-102-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6746,27 +6746,27 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>844.86</v>
+        <v>3342.38</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1057402-7488-CM26</t>
+          <t>1208985-87-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>794.73</v>
+        <v>1234.43</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2354-225-CM26</t>
+          <t>1057402-7105-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,22 +6873,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>777.96</v>
+        <v>844.86</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>874750-259-CM26</t>
+          <t>1057402-7488-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,22 +6934,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.607.903-4</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>7.560.370-3</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3553.36</v>
+        <v>794.73</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3268-501-CM26</t>
+          <t>2354-225-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>61.103.021-5</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>8.588.169-8</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1710.35</v>
+        <v>777.96</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3263-36-CM26</t>
+          <t>874750-259-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>70.788.300-6</t>
+          <t>61.607.903-4</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>CENTRAL ODONTOLOGICA MAGALLANES</t>
+          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+          <t>JOSÉ HERMINIO BARRIENTOS BARRIENTOS</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>78.307.990-9</t>
+          <t>7.560.370-3</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1500.57</v>
+        <v>3553.36</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3241-213-CM26</t>
+          <t>3268-501-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.102.028-7</t>
+          <t>61.103.021-5</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+          <t>IVª Brigada Aérea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>IVÁN DAMIR STIPICIC MATIC</t>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>8.588.169-8</t>
+          <t>78.307.990-9</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>1998.05</v>
+        <v>1710.35</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5394-442-CM26</t>
+          <t>3263-36-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>71.133.700-8</t>
+          <t>70.788.300-6</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE MAGALLANES</t>
+          <t>CENTRAL ODONTOLOGICA MAGALLANES</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7218,6 +7218,128 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
+        <v>1500.57</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>3241-213-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>61.102.028-7</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>DEPTO BIENESTAR SOCIAL (M) 3RA ZONA NAVA</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>IVÁN DAMIR STIPICIC MATIC</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>8.588.169-8</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>1998.05</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>5394-442-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>71.133.700-8</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE MAGALLANES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>78.307.990-9</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
         <v>9558.85</v>
       </c>
     </row>
